--- a/Documents/APP/20250916_dicovar_reflexion_e3n.xlsx
+++ b/Documents/APP/20250916_dicovar_reflexion_e3n.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49B2BF6-BE47-4F78-8F0B-3848E0E5BC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5D6390-F11A-4C35-9118-4C4DC05898B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5830,55 +5830,55 @@
     <t>Questionnaire Q13</t>
   </si>
   <si>
-    <t>Documents\APP\pdf\E3N_Q1.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q2.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q3_sante.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q3_alimentaire.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q4.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q5.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q6.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q7.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q8_sante.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q9.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q10.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q11.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q12.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E3N_Q13.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E4N-G1_Q1.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E4N-G1_Q2.pdf</t>
-  </si>
-  <si>
-    <t>Documents\APP\pdf\E4N-G1_Q3.pdf</t>
+    <t>Documents/APP/pdf/E3N_Q1.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q2.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q3_sante.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q3_alimentaire.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q4.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q5.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q6.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q7.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q8_sante.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q9.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q10.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q11.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q12.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E3N_Q13.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E4N-G1_Q1.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E4N-G1_Q2.pdf</t>
+  </si>
+  <si>
+    <t>Documents/APP/pdf/E4N-G1_Q3.pdf</t>
   </si>
 </sst>
 </file>
@@ -28403,7 +28403,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>1816</v>
       </c>
@@ -28426,7 +28426,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>1816</v>
       </c>

--- a/Documents/APP/20250916_dicovar_reflexion_e3n.xlsx
+++ b/Documents/APP/20250916_dicovar_reflexion_e3n.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5D6390-F11A-4C35-9118-4C4DC05898B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D88E64-EF0B-4C5E-BB08-D7388A6DAC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Documents/APP/20250916_dicovar_reflexion_e3n.xlsx
+++ b/Documents/APP/20250916_dicovar_reflexion_e3n.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D88E64-EF0B-4C5E-BB08-D7388A6DAC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6DF592-5552-41CA-91A8-7162387AC441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3645" uniqueCount="1868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1870">
   <si>
     <t>Anthropométrie</t>
   </si>
@@ -5830,55 +5830,61 @@
     <t>Questionnaire Q13</t>
   </si>
   <si>
-    <t>Documents/APP/pdf/E3N_Q1.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q2.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q3_sante.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q3_alimentaire.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q4.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q5.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q6.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q7.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q8_sante.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q9.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q10.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q11.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q12.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E3N_Q13.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E4N-G1_Q1.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E4N-G1_Q2.pdf</t>
-  </si>
-  <si>
-    <t>Documents/APP/pdf/E4N-G1_Q3.pdf</t>
+    <t>url_pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q1.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q2.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q3_sante.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q3_alimentaire.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q4.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q5.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q6.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q7.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q8_sante.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q9.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q10.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q11.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q12.pdf</t>
+  </si>
+  <si>
+    <t>E3N_Q13.pdf</t>
+  </si>
+  <si>
+    <t>E4N-G1_Q1.pdf</t>
+  </si>
+  <si>
+    <t>E4N-G1_Q2.pdf</t>
+  </si>
+  <si>
+    <t>E4N-G1_Q3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.e3n-generations.fr/sites/default/files/inline-files/</t>
   </si>
 </sst>
 </file>
@@ -28326,15 +28332,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADAAACF-4852-489C-98BC-84F18B73124B}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="7" width="28.109375" customWidth="1"/>
+    <col min="5" max="8" width="28.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>26</v>
       </c>
@@ -28351,13 +28357,16 @@
         <v>1814</v>
       </c>
       <c r="F1" s="22" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>1831</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>1825</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -28374,13 +28383,16 @@
         <v>1819</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>1851</v>
-      </c>
-      <c r="G2" s="24" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>1852</v>
+      </c>
+      <c r="H2" s="24" t="s">
         <v>1826</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -28397,13 +28409,16 @@
         <v>1820</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>1852</v>
-      </c>
-      <c r="G3" s="24" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>1853</v>
+      </c>
+      <c r="H3" s="24" t="s">
         <v>1827</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>1816</v>
       </c>
@@ -28420,13 +28435,16 @@
         <v>1822</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>1853</v>
-      </c>
-      <c r="G4" s="24" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H4" s="24" t="s">
         <v>1828</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>1816</v>
       </c>
@@ -28443,13 +28461,16 @@
         <v>1823</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>1854</v>
-      </c>
-      <c r="G5" s="24" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>1855</v>
+      </c>
+      <c r="H5" s="24" t="s">
         <v>1828</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
         <v>3</v>
       </c>
@@ -28466,13 +28487,16 @@
         <v>1821</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>1855</v>
-      </c>
-      <c r="G6" s="24" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H6" s="24" t="s">
         <v>1829</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>4</v>
       </c>
@@ -28489,11 +28513,14 @@
         <v>1842</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>1856</v>
-      </c>
-      <c r="G7" s="24"/>
-    </row>
-    <row r="8" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>1857</v>
+      </c>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
         <v>5</v>
       </c>
@@ -28510,11 +28537,14 @@
         <v>1843</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>1857</v>
-      </c>
-      <c r="G8" s="24"/>
-    </row>
-    <row r="9" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H8" s="24"/>
+    </row>
+    <row r="9" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
         <v>6</v>
       </c>
@@ -28531,11 +28561,14 @@
         <v>1844</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G9" s="24"/>
-    </row>
-    <row r="10" spans="1:7" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>1859</v>
+      </c>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="23" t="s">
         <v>7</v>
       </c>
@@ -28552,11 +28585,14 @@
         <v>1845</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>1859</v>
-      </c>
-      <c r="G10" s="24"/>
-    </row>
-    <row r="11" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H10" s="24"/>
+    </row>
+    <row r="11" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="23" t="s">
         <v>8</v>
       </c>
@@ -28573,11 +28609,14 @@
         <v>1846</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G11" s="24"/>
-    </row>
-    <row r="12" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H11" s="24"/>
+    </row>
+    <row r="12" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="23" t="s">
         <v>9</v>
       </c>
@@ -28594,10 +28633,13 @@
         <v>1847</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
         <v>10</v>
       </c>
@@ -28614,10 +28656,13 @@
         <v>1848</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="23" t="s">
         <v>11</v>
       </c>
@@ -28634,10 +28679,13 @@
         <v>1849</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="23" t="s">
         <v>1762</v>
       </c>
@@ -28654,10 +28702,13 @@
         <v>1850</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="23" t="s">
         <v>1</v>
       </c>
@@ -28674,13 +28725,16 @@
         <v>1819</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>1865</v>
-      </c>
-      <c r="G16" s="24" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H16" s="24" t="s">
         <v>1830</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="23" t="s">
         <v>2</v>
       </c>
@@ -28697,10 +28751,13 @@
         <v>1820</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1869</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
         <v>1816</v>
       </c>
@@ -28717,7 +28774,10 @@
         <v>1832</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>1867</v>
+        <v>1869</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>1868</v>
       </c>
     </row>
   </sheetData>
